--- a/tame_output/ON/bt/strategyON_20241012.xlsx
+++ b/tame_output/ON/bt/strategyON_20241012.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.4%</t>
+          <t>101.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.4%</t>
+          <t>423.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.8%</t>
+          <t>-675.7%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-123.8%</t>
+          <t>-123.7%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2113"/>
+  <dimension ref="A1:G2114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50144,7 +50144,7 @@
         <v>45575</v>
       </c>
       <c r="B2113" t="n">
-        <v>3.78896214346813</v>
+        <v>3.787848208087226</v>
       </c>
       <c r="C2113" t="n">
         <v>4.582101927173098</v>
@@ -50160,6 +50160,29 @@
       </c>
       <c r="G2113" t="n">
         <v>5.243401892419971</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>3.8192265973408</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>4.582052691606203</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>-5.141228625874381</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>2.525204816942703</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>1.102166608744787</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>5.243352656853075</v>
       </c>
     </row>
   </sheetData>
